--- a/data/trans_orig/IP04D$individual-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$individual-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>41354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>50362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50680</t>
+          <t>50738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82993</t>
+          <t>83195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98630</t>
+          <t>98445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>34709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37969</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57620</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75999</t>
+          <t>76218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89085</t>
+          <t>89215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90355</t>
+          <t>90171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156325</t>
+          <t>156750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175976</t>
+          <t>176383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21711</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>57844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62211</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100949</t>
+          <t>101345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117721</t>
+          <t>117917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21761</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>36714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44453</t>
+          <t>45110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65860</t>
+          <t>65368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45959</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45205</t>
+          <t>45520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60473</t>
+          <t>60293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94135</t>
+          <t>94627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115542</t>
+          <t>114885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28929</t>
+          <t>28568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>28075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39885</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>62085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>75322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45614</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53147</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80449</t>
+          <t>81361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95987</t>
+          <t>96734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>24574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51228</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74588</t>
+          <t>73412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101033</t>
+          <t>100748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117143</t>
+          <t>117377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104433</t>
+          <t>103877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121312</t>
+          <t>121165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209869</t>
+          <t>211045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233229</t>
+          <t>234958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65403</t>
+          <t>65231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85973</t>
+          <t>86195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>80994</t>
+          <t>81504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102441</t>
+          <t>102774</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152101</t>
+          <t>152428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181882</t>
+          <t>182314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>77723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98515</t>
+          <t>98687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68874</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90321</t>
+          <t>89811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153351</t>
+          <t>152919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183132</t>
+          <t>182805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181701</t>
+          <t>179896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221031</t>
+          <t>219776</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>217052</t>
+          <t>217360</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258778</t>
+          <t>259166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>407801</t>
+          <t>409122</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>466932</t>
+          <t>467887</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>487261</t>
+          <t>488516</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>526591</t>
+          <t>528396</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>493447</t>
+          <t>493059</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>535173</t>
+          <t>534865</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>993585</t>
+          <t>992630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1052716</t>
+          <t>1051395</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39421</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>57169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37146</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49636</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64738</t>
+          <t>64664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82412</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>71333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94022</t>
+          <t>94705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55351</t>
+          <t>54677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71045</t>
+          <t>71285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>59588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76890</t>
+          <t>76259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120208</t>
+          <t>119525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143982</t>
+          <t>142897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>62751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103928</t>
+          <t>105079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>119237</t>
+          <t>119579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35834</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45536</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65935</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103057</t>
+          <t>102836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121476</t>
+          <t>121845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39458</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44055</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>72813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82709</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>24924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>29841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46603</t>
+          <t>46893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>40050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>45595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65409</t>
+          <t>65119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>30294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48698</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>62085</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89282</t>
+          <t>88270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107545</t>
+          <t>107100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91212</t>
+          <t>92475</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109844</t>
+          <t>109616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>187230</t>
+          <t>188242</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>212362</t>
+          <t>214427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67573</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64968</t>
+          <t>64644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99972</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126924</t>
+          <t>127233</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96603</t>
+          <t>95974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115697</t>
+          <t>115257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105210</t>
+          <t>105534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125341</t>
+          <t>125411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>207430</t>
+          <t>207121</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>234382</t>
+          <t>235373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>202173</t>
+          <t>203027</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>242461</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190319</t>
+          <t>193406</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>232392</t>
+          <t>234009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>409889</t>
+          <t>405192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465742</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>457720</t>
+          <t>457958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498008</t>
+          <t>497154</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>507619</t>
+          <t>506002</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>549692</t>
+          <t>546605</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>974450</t>
+          <t>977031</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1030303</t>
+          <t>1035000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28497</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>41423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43184</t>
+          <t>43379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65250</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53886</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87398</t>
+          <t>86119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>109269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122263</t>
+          <t>122232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122854</t>
+          <t>122772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>126951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247287</t>
+          <t>247882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253973</t>
+          <t>253845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50652</t>
+          <t>50375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60197</t>
+          <t>60236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95299</t>
+          <t>94948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>108412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40780</t>
+          <t>39756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>34369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58658</t>
+          <t>59196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65828</t>
+          <t>64849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96146</t>
+          <t>97140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>29388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43057</t>
+          <t>43219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44589</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81450</t>
+          <t>82429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71930</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>38019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49095</t>
+          <t>48639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78582</t>
+          <t>78561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91816</t>
+          <t>91750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>36510</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60185</t>
+          <t>61194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62883</t>
+          <t>64266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93988</t>
+          <t>93621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83836</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101197</t>
+          <t>101311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94884</t>
+          <t>93875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119132</t>
+          <t>118559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185589</t>
+          <t>185956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216694</t>
+          <t>215311</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121968</t>
+          <t>121569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129383</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>144902</t>
+          <t>144785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153287</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>270091</t>
+          <t>270166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280922</t>
+          <t>280927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>89346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>123999</t>
+          <t>126675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>191362</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>234280</t>
+          <t>232576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>303437</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>541157</t>
+          <t>538481</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>577763</t>
+          <t>575810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>568960</t>
+          <t>570331</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>626253</t>
+          <t>625776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1122040</t>
+          <t>1124560</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1191197</t>
+          <t>1192901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
